--- a/data/03-21-densitySLF.xlsx
+++ b/data/03-21-densitySLF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/819f14cd63a8f0d1/Masterarbeit-Jil_Lehnert/03-21-Messung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\SMP-SignalProcessing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{C6367F0E-25BA-4824-87E5-9A353D3470A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61BE4AF-E871-43D9-AEAA-D43BFDF31B2C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4E3819-EC62-4BCD-AD6E-08EF16911183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7A7285C1-D9A2-4551-818D-630E300FD99C}"/>
+    <workbookView xWindow="-14505" yWindow="60" windowWidth="14610" windowHeight="15585" xr2:uid="{7A7285C1-D9A2-4551-818D-630E300FD99C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>snowdepth</t>
   </si>
@@ -48,6 +48,18 @@
   </si>
   <si>
     <t>density SLF in kg/m^3</t>
+  </si>
+  <si>
+    <t>density1</t>
+  </si>
+  <si>
+    <t>density2</t>
+  </si>
+  <si>
+    <t>density3</t>
+  </si>
+  <si>
+    <t>density4</t>
   </si>
 </sst>
 </file>
@@ -431,10 +443,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BD4604-9AC9-4BAA-9AD8-3A8771DE1EBC}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,10 +457,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>3.5</v>
       </c>
@@ -462,7 +486,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>8.5</v>
       </c>
@@ -476,7 +500,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>13.5</v>
       </c>
@@ -490,7 +514,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>18.5</v>
       </c>
@@ -504,7 +528,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>23.5</v>
       </c>
@@ -518,7 +542,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>28.5</v>
       </c>
@@ -532,7 +556,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>33.5</v>
       </c>
@@ -546,7 +570,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>38.5</v>
       </c>
@@ -560,7 +584,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>43.5</v>
       </c>
@@ -574,7 +598,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>48.5</v>
       </c>
@@ -588,7 +612,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>53.5</v>
       </c>
@@ -602,7 +626,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>58.5</v>
       </c>
@@ -616,7 +640,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>63.5</v>
       </c>
@@ -630,7 +654,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>68.5</v>
       </c>
@@ -644,7 +668,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>73.5</v>
       </c>
